--- a/output/roomself_excel/3604.xlsx
+++ b/output/roomself_excel/3604.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>27784</v>
+        <v>90998</v>
       </c>
       <c r="D2" t="n">
-        <v>1340</v>
+        <v>2436</v>
       </c>
       <c r="E2" t="n">
-        <v>220</v>
+        <v>263</v>
       </c>
       <c r="F2" t="n">
-        <v>169</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>416465</v>
+        <v>178503</v>
       </c>
       <c r="D3" t="n">
-        <v>6072</v>
+        <v>3988</v>
       </c>
       <c r="E3" t="n">
-        <v>757</v>
+        <v>390</v>
       </c>
       <c r="F3" t="n">
-        <v>721</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>722464</v>
+        <v>121204</v>
       </c>
       <c r="D4" t="n">
-        <v>6800</v>
+        <v>2800</v>
       </c>
       <c r="E4" t="n">
-        <v>880</v>
+        <v>415</v>
       </c>
       <c r="F4" t="n">
-        <v>856</v>
+        <v>343</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>235476</v>
+        <v>125136</v>
       </c>
       <c r="D5" t="n">
-        <v>4492</v>
+        <v>2848</v>
       </c>
       <c r="E5" t="n">
-        <v>880</v>
+        <v>425</v>
       </c>
       <c r="F5" t="n">
-        <v>279</v>
+        <v>345</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>481080</v>
+        <v>58232</v>
       </c>
       <c r="D6" t="n">
-        <v>5656</v>
+        <v>2040</v>
       </c>
       <c r="E6" t="n">
-        <v>880</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>570</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>475172</v>
+        <v>28224</v>
       </c>
       <c r="D7" t="n">
-        <v>5628</v>
+        <v>1356</v>
       </c>
       <c r="E7" t="n">
-        <v>880</v>
+        <v>192</v>
       </c>
       <c r="F7" t="n">
-        <v>563</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3182</v>
+        <v>60140</v>
       </c>
       <c r="D8" t="n">
-        <v>468</v>
+        <v>2172</v>
       </c>
       <c r="E8" t="n">
-        <v>43</v>
+        <v>345</v>
       </c>
       <c r="F8" t="n">
-        <v>18</v>
+        <v>213</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10434</v>
+        <v>25683</v>
       </c>
       <c r="D9" t="n">
-        <v>860</v>
+        <v>1620</v>
       </c>
       <c r="E9" t="n">
-        <v>141</v>
+        <v>198</v>
       </c>
       <c r="F9" t="n">
-        <v>18</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10">
@@ -646,16 +646,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16779</v>
+        <v>27784</v>
       </c>
       <c r="D10" t="n">
-        <v>1040</v>
+        <v>1340</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11">
@@ -668,16 +668,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>15113</v>
+        <v>416465</v>
       </c>
       <c r="D11" t="n">
-        <v>984</v>
+        <v>6072</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>757</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>721</v>
       </c>
     </row>
     <row r="12">
@@ -690,16 +690,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5369</v>
+        <v>722464</v>
       </c>
       <c r="D12" t="n">
-        <v>600</v>
+        <v>6800</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>880</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>856</v>
       </c>
     </row>
     <row r="13">
@@ -712,16 +712,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>67923</v>
+        <v>235476</v>
       </c>
       <c r="D13" t="n">
-        <v>2120</v>
+        <v>4492</v>
       </c>
       <c r="E13" t="n">
-        <v>298</v>
+        <v>880</v>
       </c>
       <c r="F13" t="n">
-        <v>268</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14">
@@ -734,16 +734,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>48178</v>
+        <v>481080</v>
       </c>
       <c r="D14" t="n">
-        <v>1756</v>
+        <v>5656</v>
       </c>
       <c r="E14" t="n">
-        <v>28</v>
+        <v>880</v>
       </c>
       <c r="F14" t="n">
-        <v>18</v>
+        <v>570</v>
       </c>
     </row>
     <row r="15">
@@ -756,16 +756,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>88328</v>
+        <v>475172</v>
       </c>
       <c r="D15" t="n">
-        <v>2424</v>
+        <v>5628</v>
       </c>
       <c r="E15" t="n">
-        <v>165</v>
+        <v>880</v>
       </c>
       <c r="F15" t="n">
-        <v>12</v>
+        <v>563</v>
       </c>
     </row>
     <row r="16">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>38340</v>
+        <v>3182</v>
       </c>
       <c r="D16" t="n">
-        <v>1676</v>
+        <v>468</v>
       </c>
       <c r="E16" t="n">
-        <v>284</v>
+        <v>43</v>
       </c>
       <c r="F16" t="n">
         <v>18</v>
@@ -800,16 +800,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>546406</v>
+        <v>10434</v>
       </c>
       <c r="D17" t="n">
-        <v>7568</v>
+        <v>860</v>
       </c>
       <c r="E17" t="n">
-        <v>1195</v>
+        <v>141</v>
       </c>
       <c r="F17" t="n">
-        <v>921</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18">
@@ -822,16 +822,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>26784</v>
+        <v>16779</v>
       </c>
       <c r="D18" t="n">
-        <v>1500</v>
+        <v>1040</v>
       </c>
       <c r="E18" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -844,16 +844,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>27930</v>
+        <v>15113</v>
       </c>
       <c r="D19" t="n">
-        <v>1372</v>
+        <v>984</v>
       </c>
       <c r="E19" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -862,20 +862,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>121204</v>
+        <v>5369</v>
       </c>
       <c r="D20" t="n">
-        <v>2800</v>
+        <v>600</v>
       </c>
       <c r="E20" t="n">
-        <v>415</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -884,20 +884,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>269501</v>
+        <v>67923</v>
       </c>
       <c r="D21" t="n">
-        <v>5800</v>
+        <v>2120</v>
       </c>
       <c r="E21" t="n">
-        <v>904</v>
+        <v>298</v>
       </c>
       <c r="F21" t="n">
-        <v>847</v>
+        <v>268</v>
       </c>
     </row>
     <row r="22">
@@ -906,20 +906,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>125136</v>
+        <v>48178</v>
       </c>
       <c r="D22" t="n">
-        <v>2848</v>
+        <v>1756</v>
       </c>
       <c r="E22" t="n">
-        <v>425</v>
+        <v>28</v>
       </c>
       <c r="F22" t="n">
-        <v>345</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -932,16 +932,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>37087</v>
+        <v>88328</v>
       </c>
       <c r="D23" t="n">
-        <v>1668</v>
+        <v>2424</v>
       </c>
       <c r="E23" t="n">
-        <v>259</v>
+        <v>165</v>
       </c>
       <c r="F23" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
@@ -954,13 +954,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>59010</v>
+        <v>38340</v>
       </c>
       <c r="D24" t="n">
-        <v>1964</v>
+        <v>1676</v>
       </c>
       <c r="E24" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F24" t="n">
         <v>18</v>
@@ -972,20 +972,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>58232</v>
+        <v>546406</v>
       </c>
       <c r="D25" t="n">
-        <v>2040</v>
+        <v>7568</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>921</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>897</v>
       </c>
     </row>
     <row r="26">
@@ -998,16 +998,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>171539</v>
+        <v>26784</v>
       </c>
       <c r="D26" t="n">
-        <v>3468</v>
+        <v>1500</v>
       </c>
       <c r="E26" t="n">
-        <v>500</v>
+        <v>279</v>
       </c>
       <c r="F26" t="n">
-        <v>413</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27">
@@ -1016,20 +1016,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>60140</v>
+        <v>27930</v>
       </c>
       <c r="D27" t="n">
-        <v>2172</v>
+        <v>1372</v>
       </c>
       <c r="E27" t="n">
-        <v>345</v>
+        <v>133</v>
       </c>
       <c r="F27" t="n">
-        <v>213</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28">
@@ -1038,20 +1038,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>28224</v>
+        <v>37087</v>
       </c>
       <c r="D28" t="n">
-        <v>1356</v>
+        <v>1668</v>
       </c>
       <c r="E28" t="n">
-        <v>192</v>
+        <v>259</v>
       </c>
       <c r="F28" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29">
@@ -1064,16 +1064,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>79616</v>
+        <v>59010</v>
       </c>
       <c r="D29" t="n">
-        <v>2308</v>
+        <v>1964</v>
       </c>
       <c r="E29" t="n">
-        <v>316</v>
+        <v>281</v>
       </c>
       <c r="F29" t="n">
-        <v>297</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30">
@@ -1082,20 +1082,42 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>25683</v>
+        <v>171539</v>
       </c>
       <c r="D30" t="n">
-        <v>1620</v>
+        <v>3468</v>
       </c>
       <c r="E30" t="n">
-        <v>198</v>
+        <v>500</v>
       </c>
       <c r="F30" t="n">
-        <v>176</v>
+        <v>413</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>79616</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2308</v>
+      </c>
+      <c r="E31" t="n">
+        <v>316</v>
+      </c>
+      <c r="F31" t="n">
+        <v>297</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/3604.xlsx
+++ b/output/roomself_excel/3604.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,12 +495,20 @@
       <c r="D2" t="n">
         <v>2436</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>263</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>29</v>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +525,20 @@
       <c r="D3" t="n">
         <v>3988</v>
       </c>
-      <c r="E3" t="n">
-        <v>390</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>230</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="G3" t="n">
+        <v>17</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,11 +555,27 @@
       <c r="D4" t="n">
         <v>2800</v>
       </c>
-      <c r="E4" t="n">
-        <v>415</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>343</v>
+        <v>314</v>
+      </c>
+      <c r="G4" t="n">
+        <v>29</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>386</v>
+      </c>
+      <c r="J4" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="5">
@@ -541,11 +593,27 @@
       <c r="D5" t="n">
         <v>2848</v>
       </c>
-      <c r="E5" t="n">
-        <v>425</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>345</v>
+        <v>316</v>
+      </c>
+      <c r="G5" t="n">
+        <v>29</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>396</v>
+      </c>
+      <c r="J5" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="6">
@@ -563,12 +631,12 @@
       <c r="D6" t="n">
         <v>2040</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +653,20 @@
       <c r="D7" t="n">
         <v>1356</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>192</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>29</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +683,20 @@
       <c r="D8" t="n">
         <v>2172</v>
       </c>
-      <c r="E8" t="n">
-        <v>345</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>213</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="G8" t="n">
+        <v>17</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,11 +713,27 @@
       <c r="D9" t="n">
         <v>1620</v>
       </c>
-      <c r="E9" t="n">
-        <v>198</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>176</v>
+        <v>169</v>
+      </c>
+      <c r="G9" t="n">
+        <v>29</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>147</v>
+      </c>
+      <c r="J9" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -651,11 +751,27 @@
       <c r="D10" t="n">
         <v>1340</v>
       </c>
-      <c r="E10" t="n">
-        <v>220</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>169</v>
+        <v>302</v>
+      </c>
+      <c r="G10" t="n">
+        <v>18</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>184</v>
+      </c>
+      <c r="J10" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="11">
@@ -673,11 +789,27 @@
       <c r="D11" t="n">
         <v>6072</v>
       </c>
-      <c r="E11" t="n">
-        <v>757</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>721</v>
+        <v>570</v>
+      </c>
+      <c r="G11" t="n">
+        <v>18</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>436</v>
+      </c>
+      <c r="J11" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="12">
@@ -695,12 +827,20 @@
       <c r="D12" t="n">
         <v>6800</v>
       </c>
-      <c r="E12" t="n">
-        <v>880</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>856</v>
-      </c>
+        <v>1701</v>
+      </c>
+      <c r="G12" t="n">
+        <v>18</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +857,20 @@
       <c r="D13" t="n">
         <v>4492</v>
       </c>
-      <c r="E13" t="n">
-        <v>880</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F13" t="n">
-        <v>279</v>
-      </c>
+        <v>558</v>
+      </c>
+      <c r="G13" t="n">
+        <v>18</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +887,20 @@
       <c r="D14" t="n">
         <v>5656</v>
       </c>
-      <c r="E14" t="n">
-        <v>880</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>570</v>
-      </c>
+        <v>1140</v>
+      </c>
+      <c r="G14" t="n">
+        <v>18</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,11 +917,27 @@
       <c r="D15" t="n">
         <v>5628</v>
       </c>
-      <c r="E15" t="n">
-        <v>880</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>563</v>
+        <v>1126</v>
+      </c>
+      <c r="G15" t="n">
+        <v>18</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>844</v>
+      </c>
+      <c r="J15" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="16">
@@ -783,12 +955,20 @@
       <c r="D16" t="n">
         <v>468</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
         <v>43</v>
       </c>
-      <c r="F16" t="n">
-        <v>18</v>
-      </c>
+      <c r="G16" t="n">
+        <v>18</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +985,20 @@
       <c r="D17" t="n">
         <v>860</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
         <v>141</v>
       </c>
-      <c r="F17" t="n">
-        <v>18</v>
-      </c>
+      <c r="G17" t="n">
+        <v>18</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +1015,12 @@
       <c r="D18" t="n">
         <v>1040</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +1037,12 @@
       <c r="D19" t="n">
         <v>984</v>
       </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +1059,12 @@
       <c r="D20" t="n">
         <v>600</v>
       </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,11 +1081,27 @@
       <c r="D21" t="n">
         <v>2120</v>
       </c>
-      <c r="E21" t="n">
-        <v>298</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F21" t="n">
-        <v>268</v>
+        <v>250</v>
+      </c>
+      <c r="G21" t="n">
+        <v>18</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>280</v>
+      </c>
+      <c r="J21" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="22">
@@ -915,12 +1119,20 @@
       <c r="D22" t="n">
         <v>1756</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
         <v>28</v>
       </c>
-      <c r="F22" t="n">
-        <v>18</v>
-      </c>
+      <c r="G22" t="n">
+        <v>18</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -937,12 +1149,12 @@
       <c r="D23" t="n">
         <v>2424</v>
       </c>
-      <c r="E23" t="n">
-        <v>165</v>
-      </c>
-      <c r="F23" t="n">
-        <v>12</v>
-      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -959,12 +1171,20 @@
       <c r="D24" t="n">
         <v>1676</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
         <v>284</v>
       </c>
-      <c r="F24" t="n">
-        <v>18</v>
-      </c>
+      <c r="G24" t="n">
+        <v>18</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -981,11 +1201,27 @@
       <c r="D25" t="n">
         <v>7568</v>
       </c>
-      <c r="E25" t="n">
-        <v>921</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F25" t="n">
-        <v>897</v>
+        <v>710</v>
+      </c>
+      <c r="G25" t="n">
+        <v>18</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>575</v>
+      </c>
+      <c r="J25" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="26">
@@ -1003,12 +1239,20 @@
       <c r="D26" t="n">
         <v>1500</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
         <v>279</v>
       </c>
-      <c r="F26" t="n">
-        <v>18</v>
-      </c>
+      <c r="G26" t="n">
+        <v>18</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1025,12 +1269,20 @@
       <c r="D27" t="n">
         <v>1372</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
         <v>133</v>
       </c>
-      <c r="F27" t="n">
-        <v>18</v>
-      </c>
+      <c r="G27" t="n">
+        <v>18</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1047,12 +1299,20 @@
       <c r="D28" t="n">
         <v>1668</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
         <v>259</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>36</v>
       </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1069,12 +1329,20 @@
       <c r="D29" t="n">
         <v>1964</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
         <v>281</v>
       </c>
-      <c r="F29" t="n">
-        <v>18</v>
-      </c>
+      <c r="G29" t="n">
+        <v>18</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1091,11 +1359,27 @@
       <c r="D30" t="n">
         <v>3468</v>
       </c>
-      <c r="E30" t="n">
-        <v>500</v>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F30" t="n">
-        <v>413</v>
+        <v>396</v>
+      </c>
+      <c r="G30" t="n">
+        <v>29</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>471</v>
+      </c>
+      <c r="J30" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="31">
@@ -1113,11 +1397,27 @@
       <c r="D31" t="n">
         <v>2308</v>
       </c>
-      <c r="E31" t="n">
-        <v>316</v>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F31" t="n">
-        <v>297</v>
+        <v>279</v>
+      </c>
+      <c r="G31" t="n">
+        <v>18</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>298</v>
+      </c>
+      <c r="J31" t="n">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/3604.xlsx
+++ b/output/roomself_excel/3604.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,46 @@
           <t>ExtWallWidth_2</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -509,6 +549,14 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -539,6 +587,14 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -577,6 +633,26 @@
       <c r="J4" t="n">
         <v>29</v>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>168</v>
+      </c>
+      <c r="N4" t="n">
+        <v>29</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -613,6 +689,38 @@
         <v>396</v>
       </c>
       <c r="J5" t="n">
+        <v>29</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>69</v>
+      </c>
+      <c r="N5" t="n">
+        <v>29</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>240</v>
+      </c>
+      <c r="R5" t="n">
         <v>29</v>
       </c>
     </row>
@@ -637,6 +745,14 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -667,6 +783,14 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -697,6 +821,26 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>86</v>
+      </c>
+      <c r="N8" t="n">
+        <v>17</v>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -735,6 +879,14 @@
       <c r="J9" t="n">
         <v>17</v>
       </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -773,6 +925,26 @@
       <c r="J10" t="n">
         <v>18</v>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>71</v>
+      </c>
+      <c r="N10" t="n">
+        <v>18</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -811,6 +983,26 @@
       <c r="J11" t="n">
         <v>18</v>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>124</v>
+      </c>
+      <c r="N11" t="n">
+        <v>18</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -841,6 +1033,26 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>481</v>
+      </c>
+      <c r="N12" t="n">
+        <v>18</v>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -871,6 +1083,14 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -901,6 +1121,26 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>260</v>
+      </c>
+      <c r="N14" t="n">
+        <v>18</v>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -939,6 +1179,26 @@
       <c r="J15" t="n">
         <v>16</v>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>334</v>
+      </c>
+      <c r="N15" t="n">
+        <v>18</v>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -969,6 +1229,14 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -999,6 +1267,14 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1021,6 +1297,14 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1043,6 +1327,14 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1065,6 +1357,14 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1103,6 +1403,14 @@
       <c r="J21" t="n">
         <v>18</v>
       </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1133,6 +1441,14 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1155,6 +1471,14 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1185,6 +1509,26 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>71</v>
+      </c>
+      <c r="N24" t="n">
+        <v>18</v>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1223,6 +1567,14 @@
       <c r="J25" t="n">
         <v>18</v>
       </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1253,6 +1605,26 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>117</v>
+      </c>
+      <c r="N26" t="n">
+        <v>18</v>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1283,6 +1655,14 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1313,6 +1693,26 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>65</v>
+      </c>
+      <c r="N28" t="n">
+        <v>36</v>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1343,6 +1743,14 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1381,6 +1789,26 @@
       <c r="J30" t="n">
         <v>17</v>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>175</v>
+      </c>
+      <c r="N30" t="n">
+        <v>29</v>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1419,6 +1847,14 @@
       <c r="J31" t="n">
         <v>18</v>
       </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
